--- a/experiment1/data_processing3/exp_data/10_questions_data_added.xlsx
+++ b/experiment1/data_processing3/exp_data/10_questions_data_added.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:T42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -850,52 +850,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>433.1428571428572</v>
+        <v>681</v>
       </c>
       <c r="C7" t="n">
-        <v>440</v>
+        <v>709.52</v>
       </c>
       <c r="D7" t="n">
-        <v>406.84</v>
+        <v>723.4400000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>462.0416666666667</v>
+        <v>693.25</v>
       </c>
       <c r="F7" t="n">
-        <v>440.5185185185185</v>
+        <v>710.0769230769231</v>
       </c>
       <c r="G7" t="n">
-        <v>432.962962962963</v>
+        <v>664.5769230769231</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6875</v>
+        <v>3.625</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6875</v>
+        <v>3.5</v>
       </c>
       <c r="J7" t="n">
-        <v>6.375</v>
+        <v>4.0625</v>
       </c>
       <c r="K7" t="n">
-        <v>1.25</v>
+        <v>1.4375</v>
       </c>
       <c r="L7" t="n">
-        <v>1.375</v>
+        <v>1.125</v>
       </c>
       <c r="M7" t="n">
-        <v>4.9375</v>
+        <v>1.4375</v>
       </c>
       <c r="N7" t="n">
-        <v>6.9375</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.125</v>
+        <v>2.9375</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1875</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
         <v>19</v>
@@ -911,57 +911,57 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>396.688679245283</v>
+        <v>522.5135135135135</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>493.8571428571428</v>
+        <v>433.1428571428572</v>
       </c>
       <c r="C8" t="n">
-        <v>522.6296296296297</v>
+        <v>440</v>
       </c>
       <c r="D8" t="n">
-        <v>533.5666666666667</v>
+        <v>406.84</v>
       </c>
       <c r="E8" t="n">
-        <v>520.0645161290323</v>
+        <v>462.0416666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>516.28</v>
+        <v>440.5185185185185</v>
       </c>
       <c r="G8" t="n">
-        <v>528.375</v>
+        <v>432.962962962963</v>
       </c>
       <c r="H8" t="n">
-        <v>6.1875</v>
+        <v>6.6875</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9375</v>
+        <v>1.6875</v>
       </c>
       <c r="J8" t="n">
-        <v>4.875</v>
+        <v>6.375</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>4.9375</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>6.9375</v>
       </c>
       <c r="O8" t="n">
-        <v>3.625</v>
+        <v>1.125</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>1.1875</v>
       </c>
       <c r="Q8" t="n">
         <v>19</v>
@@ -977,64 +977,64 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>355.6964285714286</v>
+        <v>396.688679245283</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>477.962962962963</v>
+        <v>493.8571428571428</v>
       </c>
       <c r="C9" t="n">
-        <v>533.8461538461538</v>
+        <v>522.6296296296297</v>
       </c>
       <c r="D9" t="n">
-        <v>457.68</v>
+        <v>533.5666666666667</v>
       </c>
       <c r="E9" t="n">
-        <v>484.8</v>
+        <v>520.0645161290323</v>
       </c>
       <c r="F9" t="n">
-        <v>521.5454545454545</v>
+        <v>516.28</v>
       </c>
       <c r="G9" t="n">
-        <v>499.3703703703704</v>
+        <v>528.375</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9375</v>
+        <v>6.1875</v>
       </c>
       <c r="I9" t="n">
-        <v>3.875</v>
+        <v>5.9375</v>
       </c>
       <c r="J9" t="n">
-        <v>3.875</v>
+        <v>4.875</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6875</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.375</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9375</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5625</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4375</v>
+        <v>3.625</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>423.4234234234234</v>
+        <v>355.6964285714286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>531.52</v>
+        <v>477.962962962963</v>
       </c>
       <c r="C10" t="n">
-        <v>631.625</v>
+        <v>533.8461538461538</v>
       </c>
       <c r="D10" t="n">
-        <v>534.2083333333334</v>
+        <v>457.68</v>
       </c>
       <c r="E10" t="n">
-        <v>562.16</v>
+        <v>484.8</v>
       </c>
       <c r="F10" t="n">
-        <v>651.16</v>
+        <v>521.5454545454545</v>
       </c>
       <c r="G10" t="n">
-        <v>561.7307692307693</v>
+        <v>499.3703703703704</v>
       </c>
       <c r="H10" t="n">
-        <v>6.75</v>
+        <v>3.9375</v>
       </c>
       <c r="I10" t="n">
-        <v>6.4375</v>
+        <v>3.875</v>
       </c>
       <c r="J10" t="n">
-        <v>6.8125</v>
+        <v>3.875</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2.6875</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>1.9375</v>
       </c>
       <c r="N10" t="n">
         <v>3.5625</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>3.4375</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6875</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1109,60 +1109,60 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>682</v>
+        <v>423.4234234234234</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
-        <v>526.72</v>
+        <v>540.4583333333334</v>
       </c>
       <c r="C11" t="n">
-        <v>564.88</v>
+        <v>631.625</v>
       </c>
       <c r="D11" t="n">
-        <v>522.9230769230769</v>
+        <v>534.2083333333334</v>
       </c>
       <c r="E11" t="n">
-        <v>598.36</v>
+        <v>562.16</v>
       </c>
       <c r="F11" t="n">
-        <v>568.76</v>
+        <v>651.16</v>
       </c>
       <c r="G11" t="n">
-        <v>560.9642857142857</v>
+        <v>561.7307692307693</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1875</v>
+        <v>6.75</v>
       </c>
       <c r="I11" t="n">
-        <v>4.125</v>
+        <v>6.4375</v>
       </c>
       <c r="J11" t="n">
-        <v>3.0625</v>
+        <v>6.8125</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1875</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3125</v>
+        <v>3.5625</v>
       </c>
       <c r="O11" t="n">
-        <v>3.875</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.8125</v>
+        <v>1.6875</v>
       </c>
       <c r="Q11" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1175,61 +1175,61 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>326.5090909090909</v>
+        <v>682</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B12" t="n">
+        <v>526.72</v>
+      </c>
+      <c r="C12" t="n">
+        <v>564.88</v>
+      </c>
+      <c r="D12" t="n">
+        <v>522.9230769230769</v>
+      </c>
+      <c r="E12" t="n">
+        <v>598.36</v>
+      </c>
+      <c r="F12" t="n">
+        <v>568.76</v>
+      </c>
+      <c r="G12" t="n">
+        <v>560.9642857142857</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.1875</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.125</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.0625</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.3125</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.875</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.8125</v>
+      </c>
+      <c r="Q12" t="n">
         <v>24</v>
       </c>
-      <c r="B12" t="n">
-        <v>548.5454545454545</v>
-      </c>
-      <c r="C12" t="n">
-        <v>494.7</v>
-      </c>
-      <c r="D12" t="n">
-        <v>527.8421052631579</v>
-      </c>
-      <c r="E12" t="n">
-        <v>525.4814814814815</v>
-      </c>
-      <c r="F12" t="n">
-        <v>536.4347826086956</v>
-      </c>
-      <c r="G12" t="n">
-        <v>555.4193548387096</v>
-      </c>
-      <c r="H12" t="n">
-        <v>6.625</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6.625</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5.875</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>22</v>
-      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>female</t>
@@ -1241,42 +1241,42 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>380.3461538461539</v>
+        <v>326.5090909090909</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" t="n">
-        <v>612.16</v>
+        <v>548.5454545454545</v>
       </c>
       <c r="C13" t="n">
-        <v>648.84</v>
+        <v>494.7</v>
       </c>
       <c r="D13" t="n">
-        <v>558.6666666666666</v>
+        <v>527.8421052631579</v>
       </c>
       <c r="E13" t="n">
-        <v>569.4782608695652</v>
+        <v>525.4814814814815</v>
       </c>
       <c r="F13" t="n">
-        <v>672.2727272727273</v>
+        <v>536.4347826086956</v>
       </c>
       <c r="G13" t="n">
-        <v>582.2272727272727</v>
+        <v>555.4193548387096</v>
       </c>
       <c r="H13" t="n">
-        <v>6.4375</v>
+        <v>6.625</v>
       </c>
       <c r="I13" t="n">
-        <v>1.25</v>
+        <v>6.625</v>
       </c>
       <c r="J13" t="n">
-        <v>1.125</v>
+        <v>5.875</v>
       </c>
       <c r="K13" t="n">
-        <v>1.375</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -1285,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>6.625</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -1307,64 +1307,64 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>707.77</v>
+        <v>380.3461538461539</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" t="n">
-        <v>381.5</v>
+        <v>612.16</v>
       </c>
       <c r="C14" t="n">
-        <v>393.5925925925926</v>
+        <v>648.84</v>
       </c>
       <c r="D14" t="n">
-        <v>378.92</v>
+        <v>558.6666666666666</v>
       </c>
       <c r="E14" t="n">
-        <v>411.5925925925926</v>
+        <v>569.4782608695652</v>
       </c>
       <c r="F14" t="n">
-        <v>420.5</v>
+        <v>672.2727272727273</v>
       </c>
       <c r="G14" t="n">
-        <v>389.6538461538461</v>
+        <v>582.2272727272727</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1875</v>
+        <v>6.4375</v>
       </c>
       <c r="I14" t="n">
-        <v>5.0625</v>
+        <v>1.25</v>
       </c>
       <c r="J14" t="n">
-        <v>5.0625</v>
+        <v>1.125</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>1.0625</v>
+        <v>6.625</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0625</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3125</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
         <v>22</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1373,64 +1373,64 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>249.1588785046729</v>
+        <v>707.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" t="n">
-        <v>503.6956521739131</v>
+        <v>381.5</v>
       </c>
       <c r="C15" t="n">
-        <v>585.3076923076923</v>
+        <v>393.5925925925926</v>
       </c>
       <c r="D15" t="n">
-        <v>507.2608695652174</v>
+        <v>378.92</v>
       </c>
       <c r="E15" t="n">
-        <v>477.0869565217391</v>
+        <v>411.5925925925926</v>
       </c>
       <c r="F15" t="n">
-        <v>560.6799999999999</v>
+        <v>420.5</v>
       </c>
       <c r="G15" t="n">
-        <v>483.2</v>
+        <v>389.6538461538461</v>
       </c>
       <c r="H15" t="n">
-        <v>6.1875</v>
+        <v>5.1875</v>
       </c>
       <c r="I15" t="n">
-        <v>2.375</v>
+        <v>5.0625</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3125</v>
+        <v>5.0625</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8125</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.375</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="N15" t="n">
-        <v>5.875</v>
+        <v>1.0625</v>
       </c>
       <c r="O15" t="n">
-        <v>1.375</v>
+        <v>1.0625</v>
       </c>
       <c r="P15" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="Q15" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1439,64 +1439,64 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>1365.616161616162</v>
+        <v>249.1588785046729</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" t="n">
-        <v>384.5555555555555</v>
+        <v>503.6956521739131</v>
       </c>
       <c r="C16" t="n">
-        <v>398.76</v>
+        <v>585.3076923076923</v>
       </c>
       <c r="D16" t="n">
-        <v>413.0909090909091</v>
+        <v>507.2608695652174</v>
       </c>
       <c r="E16" t="n">
-        <v>412.2352941176471</v>
+        <v>477.0869565217391</v>
       </c>
       <c r="F16" t="n">
-        <v>410.3076923076923</v>
+        <v>560.6799999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>412.9032258064516</v>
+        <v>483.2</v>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>6.1875</v>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>2.375</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>3.3125</v>
       </c>
       <c r="K16" t="n">
-        <v>1.375</v>
+        <v>2.8125</v>
       </c>
       <c r="L16" t="n">
         <v>1.375</v>
       </c>
       <c r="M16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="O16" t="n">
         <v>1.375</v>
       </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>1.625</v>
       </c>
       <c r="Q16" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -1505,48 +1505,48 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>302.4684684684685</v>
+        <v>1365.616161616162</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" t="n">
-        <v>467.3571428571428</v>
+        <v>384.5555555555555</v>
       </c>
       <c r="C17" t="n">
-        <v>491.0384615384615</v>
+        <v>398.76</v>
       </c>
       <c r="D17" t="n">
-        <v>465.6875</v>
+        <v>413.0909090909091</v>
       </c>
       <c r="E17" t="n">
-        <v>459.625</v>
+        <v>412.2352941176471</v>
       </c>
       <c r="F17" t="n">
-        <v>555.8846153846154</v>
+        <v>410.3076923076923</v>
       </c>
       <c r="G17" t="n">
-        <v>539.9545454545455</v>
+        <v>412.9032258064516</v>
       </c>
       <c r="H17" t="n">
         <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>6.4375</v>
+        <v>7</v>
       </c>
       <c r="J17" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3125</v>
+        <v>1.375</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
@@ -1555,10 +1555,10 @@
         <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4375</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -1571,60 +1571,60 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>1180.727272727273</v>
+        <v>302.4684684684685</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" t="n">
-        <v>511.1538461538461</v>
+        <v>467.3571428571428</v>
       </c>
       <c r="C18" t="n">
-        <v>484.8571428571428</v>
+        <v>491.0384615384615</v>
       </c>
       <c r="D18" t="n">
-        <v>504.9166666666667</v>
+        <v>465.6875</v>
       </c>
       <c r="E18" t="n">
-        <v>478.6086956521739</v>
+        <v>459.625</v>
       </c>
       <c r="F18" t="n">
-        <v>476.9090909090909</v>
+        <v>555.8846153846154</v>
       </c>
       <c r="G18" t="n">
-        <v>514.125</v>
+        <v>539.9545454545455</v>
       </c>
       <c r="H18" t="n">
-        <v>5.1875</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>5.25</v>
+        <v>6.4375</v>
       </c>
       <c r="J18" t="n">
-        <v>5.1875</v>
+        <v>6.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>2.5</v>
+        <v>2.3125</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>2.4375</v>
       </c>
       <c r="Q18" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -1637,126 +1637,126 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>513.2403846153846</v>
+        <v>1180.727272727273</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" t="n">
-        <v>473.0416666666667</v>
+        <v>511.1538461538461</v>
       </c>
       <c r="C19" t="n">
-        <v>495.625</v>
+        <v>484.8571428571428</v>
       </c>
       <c r="D19" t="n">
-        <v>493.44</v>
+        <v>504.9166666666667</v>
       </c>
       <c r="E19" t="n">
-        <v>427.08</v>
+        <v>478.6086956521739</v>
       </c>
       <c r="F19" t="n">
-        <v>471.1304347826087</v>
+        <v>476.9090909090909</v>
       </c>
       <c r="G19" t="n">
-        <v>564.76</v>
+        <v>514.125</v>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>5.1875</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>5.25</v>
       </c>
       <c r="J19" t="n">
-        <v>3.125</v>
+        <v>5.1875</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1875</v>
+        <v>2.5</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>2.125</v>
+        <v>2.5</v>
       </c>
       <c r="N19" t="n">
-        <v>5.5625</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.625</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>267.9716981132075</v>
+        <v>513.2403846153846</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" t="n">
-        <v>528.5599999999999</v>
+        <v>473.0416666666667</v>
       </c>
       <c r="C20" t="n">
-        <v>491</v>
+        <v>495.625</v>
       </c>
       <c r="D20" t="n">
-        <v>578.3913043478261</v>
+        <v>493.44</v>
       </c>
       <c r="E20" t="n">
-        <v>542.96</v>
+        <v>427.08</v>
       </c>
       <c r="F20" t="n">
-        <v>506.28</v>
+        <v>471.1304347826087</v>
       </c>
       <c r="G20" t="n">
-        <v>569.9642857142857</v>
+        <v>564.76</v>
       </c>
       <c r="H20" t="n">
-        <v>4.5625</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>2.375</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>2.375</v>
+        <v>3.125</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9375</v>
+        <v>2.1875</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9375</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>2.3125</v>
+        <v>2.125</v>
       </c>
       <c r="N20" t="n">
-        <v>4.625</v>
+        <v>5.5625</v>
       </c>
       <c r="O20" t="n">
-        <v>2.5625</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.625</v>
       </c>
       <c r="Q20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -1765,64 +1765,64 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>399.7090909090909</v>
+        <v>267.9716981132075</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" t="n">
-        <v>386.0344827586207</v>
+        <v>528.5599999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>380.6428571428572</v>
+        <v>491</v>
       </c>
       <c r="D21" t="n">
-        <v>402.4642857142857</v>
+        <v>578.3913043478261</v>
       </c>
       <c r="E21" t="n">
-        <v>394.9166666666667</v>
+        <v>542.96</v>
       </c>
       <c r="F21" t="n">
-        <v>429.2592592592592</v>
+        <v>506.28</v>
       </c>
       <c r="G21" t="n">
-        <v>395.9565217391304</v>
+        <v>569.9642857142857</v>
       </c>
       <c r="H21" t="n">
-        <v>6.625</v>
+        <v>4.5625</v>
       </c>
       <c r="I21" t="n">
-        <v>6.125</v>
+        <v>2.375</v>
       </c>
       <c r="J21" t="n">
-        <v>5.3125</v>
+        <v>2.375</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1875</v>
+        <v>1.9375</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>1.9375</v>
       </c>
       <c r="M21" t="n">
-        <v>1.875</v>
+        <v>2.3125</v>
       </c>
       <c r="N21" t="n">
-        <v>5.8125</v>
+        <v>4.625</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8125</v>
+        <v>2.5625</v>
       </c>
       <c r="P21" t="n">
-        <v>3.1875</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -1835,64 +1835,64 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>289.9816513761468</v>
+        <v>399.7090909090909</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" t="n">
-        <v>343.1904761904762</v>
+        <v>386.0344827586207</v>
       </c>
       <c r="C22" t="n">
-        <v>339.9230769230769</v>
+        <v>380.6428571428572</v>
       </c>
       <c r="D22" t="n">
-        <v>357.2592592592592</v>
+        <v>402.4642857142857</v>
       </c>
       <c r="E22" t="n">
-        <v>374.16</v>
+        <v>394.9166666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>383.3478260869565</v>
+        <v>429.2592592592592</v>
       </c>
       <c r="G22" t="n">
-        <v>343.6818181818182</v>
+        <v>395.9565217391304</v>
       </c>
       <c r="H22" t="n">
-        <v>5.6875</v>
+        <v>6.625</v>
       </c>
       <c r="I22" t="n">
-        <v>2.9375</v>
+        <v>6.125</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9375</v>
+        <v>5.3125</v>
       </c>
       <c r="K22" t="n">
-        <v>1.125</v>
+        <v>1.1875</v>
       </c>
       <c r="L22" t="n">
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>4.0625</v>
+        <v>1.875</v>
       </c>
       <c r="N22" t="n">
-        <v>5.125</v>
+        <v>5.8125</v>
       </c>
       <c r="O22" t="n">
-        <v>1.9375</v>
+        <v>2.8125</v>
       </c>
       <c r="P22" t="n">
-        <v>3.5</v>
+        <v>3.1875</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -1901,126 +1901,126 @@
         </is>
       </c>
       <c r="T22" t="n">
-        <v>263.4081632653061</v>
+        <v>289.9816513761468</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" t="n">
-        <v>419</v>
+        <v>350.55</v>
       </c>
       <c r="C23" t="n">
-        <v>422.9259259259259</v>
+        <v>339.9230769230769</v>
       </c>
       <c r="D23" t="n">
-        <v>468.8846153846154</v>
+        <v>363.5</v>
       </c>
       <c r="E23" t="n">
-        <v>429.6956521739131</v>
+        <v>374.16</v>
       </c>
       <c r="F23" t="n">
-        <v>479.375</v>
+        <v>371.1818181818182</v>
       </c>
       <c r="G23" t="n">
-        <v>478.08</v>
+        <v>343.6818181818182</v>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>5.6875</v>
       </c>
       <c r="I23" t="n">
-        <v>3.5625</v>
+        <v>2.9375</v>
       </c>
       <c r="J23" t="n">
-        <v>5.6875</v>
+        <v>3.9375</v>
       </c>
       <c r="K23" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4.0625</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5.125</v>
+      </c>
+      <c r="O23" t="n">
         <v>1.9375</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.9375</v>
-      </c>
-      <c r="M23" t="n">
-        <v>4.625</v>
-      </c>
-      <c r="N23" t="n">
-        <v>6.0625</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.1875</v>
-      </c>
       <c r="P23" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="T23" t="n">
-        <v>288.5462962962963</v>
+        <v>263.4081632653061</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" t="n">
-        <v>478.0952380952381</v>
+        <v>419</v>
       </c>
       <c r="C24" t="n">
-        <v>478.1739130434783</v>
+        <v>422.9259259259259</v>
       </c>
       <c r="D24" t="n">
-        <v>445.5</v>
+        <v>468.8846153846154</v>
       </c>
       <c r="E24" t="n">
-        <v>490.3103448275862</v>
+        <v>429.6956521739131</v>
       </c>
       <c r="F24" t="n">
-        <v>469.4347826086956</v>
+        <v>479.375</v>
       </c>
       <c r="G24" t="n">
-        <v>494.5</v>
+        <v>478.08</v>
       </c>
       <c r="H24" t="n">
-        <v>5.875</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
+        <v>3.5625</v>
+      </c>
+      <c r="J24" t="n">
         <v>5.6875</v>
       </c>
-      <c r="J24" t="n">
-        <v>5</v>
-      </c>
       <c r="K24" t="n">
-        <v>1.375</v>
+        <v>1.9375</v>
       </c>
       <c r="L24" t="n">
-        <v>1.25</v>
+        <v>1.9375</v>
       </c>
       <c r="M24" t="n">
-        <v>2.5</v>
+        <v>4.625</v>
       </c>
       <c r="N24" t="n">
-        <v>5.1875</v>
+        <v>6.0625</v>
       </c>
       <c r="O24" t="n">
-        <v>4.3125</v>
+        <v>2.1875</v>
       </c>
       <c r="P24" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -2033,57 +2033,57 @@
         </is>
       </c>
       <c r="T24" t="n">
-        <v>576.5436893203884</v>
+        <v>288.5462962962963</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" t="n">
-        <v>659.6296296296297</v>
+        <v>478.0952380952381</v>
       </c>
       <c r="C25" t="n">
-        <v>704.75</v>
+        <v>478.1739130434783</v>
       </c>
       <c r="D25" t="n">
-        <v>656.4074074074074</v>
+        <v>445.5</v>
       </c>
       <c r="E25" t="n">
-        <v>651.04</v>
+        <v>490.3103448275862</v>
       </c>
       <c r="F25" t="n">
-        <v>690.72</v>
+        <v>469.4347826086956</v>
       </c>
       <c r="G25" t="n">
-        <v>631.08</v>
+        <v>494.5</v>
       </c>
       <c r="H25" t="n">
-        <v>3.9375</v>
+        <v>5.875</v>
       </c>
       <c r="I25" t="n">
-        <v>3.9375</v>
+        <v>5.6875</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9375</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>4.0625</v>
+        <v>1.375</v>
       </c>
       <c r="L25" t="n">
-        <v>4.0625</v>
+        <v>1.25</v>
       </c>
       <c r="M25" t="n">
-        <v>4.0625</v>
+        <v>2.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5625</v>
+        <v>5.1875</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4375</v>
+        <v>4.3125</v>
       </c>
       <c r="P25" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q25" t="n">
         <v>21</v>
@@ -2095,64 +2095,64 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>340.4036697247706</v>
+        <v>576.5436893203884</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" t="n">
-        <v>532.2083333333334</v>
+        <v>659.6296296296297</v>
       </c>
       <c r="C26" t="n">
-        <v>634.2692307692307</v>
+        <v>704.75</v>
       </c>
       <c r="D26" t="n">
-        <v>533.2</v>
+        <v>656.4074074074074</v>
       </c>
       <c r="E26" t="n">
-        <v>614.448275862069</v>
+        <v>651.04</v>
       </c>
       <c r="F26" t="n">
-        <v>556.5185185185185</v>
+        <v>690.72</v>
       </c>
       <c r="G26" t="n">
-        <v>495</v>
+        <v>631.08</v>
       </c>
       <c r="H26" t="n">
-        <v>6.75</v>
+        <v>3.9375</v>
       </c>
       <c r="I26" t="n">
+        <v>3.9375</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.9375</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.0625</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4.0625</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4.0625</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.5625</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.4375</v>
+      </c>
+      <c r="P26" t="n">
         <v>3.5</v>
       </c>
-      <c r="J26" t="n">
-        <v>3.6875</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2.8125</v>
-      </c>
-      <c r="N26" t="n">
-        <v>6.625</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3</v>
-      </c>
-      <c r="P26" t="n">
-        <v>3.125</v>
-      </c>
       <c r="Q26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -2165,39 +2165,39 @@
         </is>
       </c>
       <c r="T26" t="n">
-        <v>515.9909090909091</v>
+        <v>340.4036697247706</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" t="n">
-        <v>469.8260869565217</v>
+        <v>532.2083333333334</v>
       </c>
       <c r="C27" t="n">
-        <v>591.0909090909091</v>
+        <v>634.2692307692307</v>
       </c>
       <c r="D27" t="n">
-        <v>533.6666666666666</v>
+        <v>533.2</v>
       </c>
       <c r="E27" t="n">
-        <v>502.7692307692308</v>
+        <v>614.448275862069</v>
       </c>
       <c r="F27" t="n">
-        <v>617.5384615384615</v>
+        <v>556.5185185185185</v>
       </c>
       <c r="G27" t="n">
-        <v>482.962962962963</v>
+        <v>495</v>
       </c>
       <c r="H27" t="n">
-        <v>6.375</v>
+        <v>6.75</v>
       </c>
       <c r="I27" t="n">
-        <v>6.3125</v>
+        <v>3.5</v>
       </c>
       <c r="J27" t="n">
-        <v>6.5</v>
+        <v>3.6875</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -2206,19 +2206,19 @@
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>2.8125</v>
       </c>
       <c r="N27" t="n">
-        <v>1.125</v>
+        <v>6.625</v>
       </c>
       <c r="O27" t="n">
-        <v>1.125</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.125</v>
+        <v>3.125</v>
       </c>
       <c r="Q27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -2231,57 +2231,57 @@
         </is>
       </c>
       <c r="T27" t="n">
-        <v>353.078431372549</v>
+        <v>515.9909090909091</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B28" t="n">
-        <v>657.4400000000001</v>
+        <v>469.8260869565217</v>
       </c>
       <c r="C28" t="n">
-        <v>572.304347826087</v>
+        <v>591.0909090909091</v>
       </c>
       <c r="D28" t="n">
-        <v>701</v>
+        <v>533.6666666666666</v>
       </c>
       <c r="E28" t="n">
-        <v>660.7857142857143</v>
+        <v>502.7692307692308</v>
       </c>
       <c r="F28" t="n">
-        <v>555.1363636363636</v>
+        <v>617.5384615384615</v>
       </c>
       <c r="G28" t="n">
-        <v>649.8846153846154</v>
+        <v>482.962962962963</v>
       </c>
       <c r="H28" t="n">
-        <v>6.5625</v>
+        <v>6.375</v>
       </c>
       <c r="I28" t="n">
-        <v>6.375</v>
+        <v>6.3125</v>
       </c>
       <c r="J28" t="n">
-        <v>5.875</v>
+        <v>6.5</v>
       </c>
       <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
         <v>1.125</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5.75</v>
-      </c>
       <c r="O28" t="n">
-        <v>2.4375</v>
+        <v>1.125</v>
       </c>
       <c r="P28" t="n">
-        <v>3.625</v>
+        <v>1.125</v>
       </c>
       <c r="Q28" t="n">
         <v>21</v>
@@ -2297,60 +2297,60 @@
         </is>
       </c>
       <c r="T28" t="n">
-        <v>523.074074074074</v>
+        <v>353.078431372549</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29" t="n">
-        <v>596.25</v>
+        <v>657.4400000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>569.8947368421053</v>
+        <v>572.304347826087</v>
       </c>
       <c r="D29" t="n">
-        <v>603.5555555555555</v>
+        <v>701</v>
       </c>
       <c r="E29" t="n">
-        <v>578.2727272727273</v>
+        <v>660.7857142857143</v>
       </c>
       <c r="F29" t="n">
-        <v>581.6190476190476</v>
+        <v>555.1363636363636</v>
       </c>
       <c r="G29" t="n">
-        <v>608.8695652173913</v>
+        <v>649.8846153846154</v>
       </c>
       <c r="H29" t="n">
-        <v>5.6875</v>
+        <v>6.5625</v>
       </c>
       <c r="I29" t="n">
-        <v>5.6875</v>
+        <v>6.375</v>
       </c>
       <c r="J29" t="n">
-        <v>5.125</v>
+        <v>5.875</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="L29" t="n">
-        <v>1.125</v>
+        <v>1.375</v>
       </c>
       <c r="M29" t="n">
-        <v>1.0625</v>
+        <v>2.625</v>
       </c>
       <c r="N29" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="O29" t="n">
-        <v>6.125</v>
+        <v>2.4375</v>
       </c>
       <c r="P29" t="n">
-        <v>5.6875</v>
+        <v>3.625</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -2363,60 +2363,60 @@
         </is>
       </c>
       <c r="T29" t="n">
-        <v>632.1862745098039</v>
+        <v>523.074074074074</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" t="n">
-        <v>399.3461538461539</v>
+        <v>596.25</v>
       </c>
       <c r="C30" t="n">
-        <v>402.625</v>
+        <v>569.8947368421053</v>
       </c>
       <c r="D30" t="n">
-        <v>389.28</v>
+        <v>603.5555555555555</v>
       </c>
       <c r="E30" t="n">
-        <v>439.16</v>
+        <v>578.2727272727273</v>
       </c>
       <c r="F30" t="n">
-        <v>483.375</v>
+        <v>581.6190476190476</v>
       </c>
       <c r="G30" t="n">
-        <v>417.3846153846154</v>
+        <v>608.8695652173913</v>
       </c>
       <c r="H30" t="n">
-        <v>5.875</v>
+        <v>5.6875</v>
       </c>
       <c r="I30" t="n">
-        <v>5.625</v>
+        <v>5.6875</v>
       </c>
       <c r="J30" t="n">
-        <v>3.4375</v>
+        <v>5.125</v>
       </c>
       <c r="K30" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.6875</v>
+        <v>1.125</v>
       </c>
       <c r="M30" t="n">
-        <v>1.75</v>
+        <v>1.0625</v>
       </c>
       <c r="N30" t="n">
-        <v>3.8125</v>
+        <v>6.25</v>
       </c>
       <c r="O30" t="n">
-        <v>2.8125</v>
+        <v>6.125</v>
       </c>
       <c r="P30" t="n">
-        <v>2.4375</v>
+        <v>5.6875</v>
       </c>
       <c r="Q30" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -2429,60 +2429,60 @@
         </is>
       </c>
       <c r="T30" t="n">
-        <v>1027.283018867925</v>
+        <v>632.1862745098039</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B31" t="n">
-        <v>480</v>
+        <v>399.3461538461539</v>
       </c>
       <c r="C31" t="n">
-        <v>479.5925925925926</v>
+        <v>402.625</v>
       </c>
       <c r="D31" t="n">
-        <v>484.9615384615385</v>
+        <v>389.28</v>
       </c>
       <c r="E31" t="n">
-        <v>508.2692307692308</v>
+        <v>439.16</v>
       </c>
       <c r="F31" t="n">
-        <v>492.8846153846154</v>
+        <v>483.375</v>
       </c>
       <c r="G31" t="n">
-        <v>483.7692307692308</v>
+        <v>417.3846153846154</v>
       </c>
       <c r="H31" t="n">
-        <v>6.5625</v>
+        <v>5.875</v>
       </c>
       <c r="I31" t="n">
+        <v>5.625</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.4375</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.6875</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.8125</v>
+      </c>
+      <c r="O31" t="n">
         <v>2.8125</v>
       </c>
-      <c r="J31" t="n">
-        <v>6.625</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.5625</v>
-      </c>
-      <c r="L31" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3.875</v>
-      </c>
-      <c r="N31" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.375</v>
-      </c>
       <c r="P31" t="n">
-        <v>4</v>
+        <v>2.4375</v>
       </c>
       <c r="Q31" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -2495,60 +2495,60 @@
         </is>
       </c>
       <c r="T31" t="n">
-        <v>566.3873873873874</v>
+        <v>1027.283018867925</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B32" t="n">
-        <v>532.3333333333334</v>
+        <v>480</v>
       </c>
       <c r="C32" t="n">
-        <v>599.6521739130435</v>
+        <v>479.5925925925926</v>
       </c>
       <c r="D32" t="n">
-        <v>541.5833333333334</v>
+        <v>484.9615384615385</v>
       </c>
       <c r="E32" t="n">
-        <v>537</v>
+        <v>508.2692307692308</v>
       </c>
       <c r="F32" t="n">
-        <v>616.7727272727273</v>
+        <v>492.8846153846154</v>
       </c>
       <c r="G32" t="n">
-        <v>579.1153846153846</v>
+        <v>483.7692307692308</v>
       </c>
       <c r="H32" t="n">
-        <v>5.3125</v>
+        <v>6.5625</v>
       </c>
       <c r="I32" t="n">
-        <v>5.25</v>
+        <v>2.8125</v>
       </c>
       <c r="J32" t="n">
-        <v>5.3125</v>
+        <v>6.625</v>
       </c>
       <c r="K32" t="n">
-        <v>5.125</v>
+        <v>3.5625</v>
       </c>
       <c r="L32" t="n">
-        <v>5.125</v>
+        <v>2.625</v>
       </c>
       <c r="M32" t="n">
-        <v>5.125</v>
+        <v>3.875</v>
       </c>
       <c r="N32" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="O32" t="n">
-        <v>5.25</v>
+        <v>2.375</v>
       </c>
       <c r="P32" t="n">
-        <v>5.125</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -2561,60 +2561,60 @@
         </is>
       </c>
       <c r="T32" t="n">
-        <v>909.2095238095238</v>
+        <v>566.3873873873874</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B33" t="n">
-        <v>422.2916666666667</v>
+        <v>532.3333333333334</v>
       </c>
       <c r="C33" t="n">
-        <v>475.0740740740741</v>
+        <v>599.6521739130435</v>
       </c>
       <c r="D33" t="n">
-        <v>471.8260869565217</v>
+        <v>541.5833333333334</v>
       </c>
       <c r="E33" t="n">
-        <v>460.551724137931</v>
+        <v>537</v>
       </c>
       <c r="F33" t="n">
-        <v>475.5769230769231</v>
+        <v>616.7727272727273</v>
       </c>
       <c r="G33" t="n">
-        <v>462</v>
+        <v>579.1153846153846</v>
       </c>
       <c r="H33" t="n">
-        <v>6.4375</v>
+        <v>5.3125</v>
       </c>
       <c r="I33" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J33" t="n">
         <v>5.3125</v>
       </c>
-      <c r="J33" t="n">
-        <v>5.5625</v>
-      </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>5.125</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>5.125</v>
       </c>
       <c r="M33" t="n">
-        <v>4.5</v>
+        <v>5.125</v>
       </c>
       <c r="N33" t="n">
-        <v>5.3125</v>
+        <v>5.25</v>
       </c>
       <c r="O33" t="n">
-        <v>1.8125</v>
+        <v>5.25</v>
       </c>
       <c r="P33" t="n">
-        <v>4.75</v>
+        <v>5.125</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -2627,60 +2627,60 @@
         </is>
       </c>
       <c r="T33" t="n">
-        <v>410.5982142857143</v>
+        <v>909.2095238095238</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34" t="n">
-        <v>492.1111111111111</v>
+        <v>422.2916666666667</v>
       </c>
       <c r="C34" t="n">
-        <v>475.4814814814815</v>
+        <v>475.0740740740741</v>
       </c>
       <c r="D34" t="n">
-        <v>452.1481481481482</v>
+        <v>471.8260869565217</v>
       </c>
       <c r="E34" t="n">
-        <v>501.0740740740741</v>
+        <v>460.551724137931</v>
       </c>
       <c r="F34" t="n">
-        <v>502.12</v>
+        <v>475.5769230769231</v>
       </c>
       <c r="G34" t="n">
-        <v>515.6296296296297</v>
+        <v>462</v>
       </c>
       <c r="H34" t="n">
-        <v>2.125</v>
+        <v>6.4375</v>
       </c>
       <c r="I34" t="n">
-        <v>3.0625</v>
+        <v>5.3125</v>
       </c>
       <c r="J34" t="n">
-        <v>4.8125</v>
+        <v>5.5625</v>
       </c>
       <c r="K34" t="n">
-        <v>2.0625</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.9375</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5625</v>
+        <v>4.5</v>
       </c>
       <c r="N34" t="n">
+        <v>5.3125</v>
+      </c>
+      <c r="O34" t="n">
         <v>1.8125</v>
       </c>
-      <c r="O34" t="n">
-        <v>1.875</v>
-      </c>
       <c r="P34" t="n">
-        <v>1.8125</v>
+        <v>4.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -2689,64 +2689,64 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="T34" t="n">
-        <v>503.0446428571428</v>
+        <v>410.5982142857143</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B35" t="n">
-        <v>569.7142857142857</v>
+        <v>492.1111111111111</v>
       </c>
       <c r="C35" t="n">
-        <v>587.12</v>
+        <v>475.4814814814815</v>
       </c>
       <c r="D35" t="n">
-        <v>594.3333333333334</v>
+        <v>452.1481481481482</v>
       </c>
       <c r="E35" t="n">
-        <v>599.4736842105264</v>
+        <v>501.0740740740741</v>
       </c>
       <c r="F35" t="n">
-        <v>655.2916666666666</v>
+        <v>502.12</v>
       </c>
       <c r="G35" t="n">
-        <v>553</v>
+        <v>515.6296296296297</v>
       </c>
       <c r="H35" t="n">
-        <v>6.6875</v>
+        <v>2.125</v>
       </c>
       <c r="I35" t="n">
-        <v>5.25</v>
+        <v>3.0625</v>
       </c>
       <c r="J35" t="n">
-        <v>3.9375</v>
+        <v>4.8125</v>
       </c>
       <c r="K35" t="n">
-        <v>1.6875</v>
+        <v>2.0625</v>
       </c>
       <c r="L35" t="n">
+        <v>1.9375</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.5625</v>
+      </c>
+      <c r="N35" t="n">
         <v>1.8125</v>
       </c>
-      <c r="M35" t="n">
-        <v>2</v>
-      </c>
-      <c r="N35" t="n">
-        <v>6.75</v>
-      </c>
       <c r="O35" t="n">
-        <v>2.125</v>
+        <v>1.875</v>
       </c>
       <c r="P35" t="n">
-        <v>2.125</v>
+        <v>1.8125</v>
       </c>
       <c r="Q35" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -2755,68 +2755,68 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="T35" t="n">
-        <v>590.7244897959183</v>
+        <v>503.0446428571428</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B36" t="n">
-        <v>399.88</v>
+        <v>569.7142857142857</v>
       </c>
       <c r="C36" t="n">
-        <v>434</v>
+        <v>587.12</v>
       </c>
       <c r="D36" t="n">
-        <v>401.2903225806452</v>
+        <v>594.3333333333334</v>
       </c>
       <c r="E36" t="n">
-        <v>434</v>
+        <v>599.4736842105264</v>
       </c>
       <c r="F36" t="n">
-        <v>433.5925925925926</v>
+        <v>655.2916666666666</v>
       </c>
       <c r="G36" t="n">
-        <v>427.6190476190476</v>
+        <v>553</v>
       </c>
       <c r="H36" t="n">
-        <v>7</v>
+        <v>6.6875</v>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="J36" t="n">
-        <v>7</v>
+        <v>3.9375</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>1.6875</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>1.8125</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="N36" t="n">
         <v>6.75</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>2.125</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>2.125</v>
       </c>
       <c r="Q36" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -2825,64 +2825,64 @@
         </is>
       </c>
       <c r="T36" t="n">
-        <v>329.8165137614679</v>
+        <v>590.7244897959183</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B37" t="n">
-        <v>628.1034482758621</v>
+        <v>399.88</v>
       </c>
       <c r="C37" t="n">
-        <v>811.7037037037037</v>
+        <v>434</v>
       </c>
       <c r="D37" t="n">
-        <v>621.8571428571429</v>
+        <v>401.2903225806452</v>
       </c>
       <c r="E37" t="n">
-        <v>627.3636363636364</v>
+        <v>434</v>
       </c>
       <c r="F37" t="n">
-        <v>723.7391304347826</v>
+        <v>433.5925925925926</v>
       </c>
       <c r="G37" t="n">
-        <v>655.1935483870968</v>
+        <v>427.6190476190476</v>
       </c>
       <c r="H37" t="n">
-        <v>6.375</v>
+        <v>7</v>
       </c>
       <c r="I37" t="n">
-        <v>6.375</v>
+        <v>7</v>
       </c>
       <c r="J37" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="K37" t="n">
-        <v>1.3125</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>1.625</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>6.0625</v>
+        <v>6.75</v>
       </c>
       <c r="O37" t="n">
-        <v>5.9375</v>
+        <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>4.75</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -2891,60 +2891,60 @@
         </is>
       </c>
       <c r="T37" t="n">
-        <v>1058.091743119266</v>
+        <v>329.8165137614679</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B38" t="n">
-        <v>423.9285714285714</v>
+        <v>628.1034482758621</v>
       </c>
       <c r="C38" t="n">
-        <v>462</v>
+        <v>811.7037037037037</v>
       </c>
       <c r="D38" t="n">
-        <v>443.125</v>
+        <v>621.8571428571429</v>
       </c>
       <c r="E38" t="n">
-        <v>420.5833333333333</v>
+        <v>627.3636363636364</v>
       </c>
       <c r="F38" t="n">
-        <v>490.6923076923077</v>
+        <v>723.7391304347826</v>
       </c>
       <c r="G38" t="n">
-        <v>432.5555555555555</v>
+        <v>655.1935483870968</v>
       </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>6.375</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1875</v>
+        <v>6.375</v>
       </c>
       <c r="J38" t="n">
-        <v>2.1875</v>
+        <v>5.75</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>1.3125</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>1.375</v>
+        <v>1.625</v>
       </c>
       <c r="N38" t="n">
-        <v>6.625</v>
+        <v>6.0625</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>5.9375</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>4.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -2957,64 +2957,64 @@
         </is>
       </c>
       <c r="T38" t="n">
-        <v>565.8130841121496</v>
+        <v>1058.091743119266</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B39" t="n">
-        <v>425.3913043478261</v>
+        <v>423.9285714285714</v>
       </c>
       <c r="C39" t="n">
-        <v>488.75</v>
+        <v>462</v>
       </c>
       <c r="D39" t="n">
-        <v>458.7407407407408</v>
+        <v>443.125</v>
       </c>
       <c r="E39" t="n">
-        <v>455.1538461538461</v>
+        <v>420.5833333333333</v>
       </c>
       <c r="F39" t="n">
-        <v>448.4230769230769</v>
+        <v>490.6923076923077</v>
       </c>
       <c r="G39" t="n">
-        <v>442.6666666666667</v>
+        <v>432.5555555555555</v>
       </c>
       <c r="H39" t="n">
-        <v>4.9375</v>
+        <v>7</v>
       </c>
       <c r="I39" t="n">
-        <v>4.875</v>
+        <v>1.1875</v>
       </c>
       <c r="J39" t="n">
-        <v>5.375</v>
+        <v>2.1875</v>
       </c>
       <c r="K39" t="n">
-        <v>1.1875</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1875</v>
+        <v>1.375</v>
       </c>
       <c r="N39" t="n">
-        <v>1.9375</v>
+        <v>6.625</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>4.0625</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -3023,64 +3023,64 @@
         </is>
       </c>
       <c r="T39" t="n">
-        <v>408.254716981132</v>
+        <v>565.8130841121496</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B40" t="n">
-        <v>599.1666666666666</v>
+        <v>436.0454545454546</v>
       </c>
       <c r="C40" t="n">
-        <v>640.2962962962963</v>
+        <v>488.75</v>
       </c>
       <c r="D40" t="n">
-        <v>654.76</v>
+        <v>458.7407407407408</v>
       </c>
       <c r="E40" t="n">
-        <v>627.3571428571429</v>
+        <v>455.1538461538461</v>
       </c>
       <c r="F40" t="n">
-        <v>627.8461538461538</v>
+        <v>448.4230769230769</v>
       </c>
       <c r="G40" t="n">
-        <v>594.4400000000001</v>
+        <v>442.6666666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>7</v>
+        <v>4.9375</v>
       </c>
       <c r="I40" t="n">
-        <v>4.5625</v>
+        <v>4.875</v>
       </c>
       <c r="J40" t="n">
-        <v>5.875</v>
+        <v>5.375</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>1.1875</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>4.1875</v>
       </c>
       <c r="N40" t="n">
-        <v>5.9375</v>
+        <v>1.9375</v>
       </c>
       <c r="O40" t="n">
-        <v>1.375</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>2.875</v>
+        <v>4.0625</v>
       </c>
       <c r="Q40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -3089,72 +3089,138 @@
         </is>
       </c>
       <c r="T40" t="n">
-        <v>317.4622641509434</v>
+        <v>408.254716981132</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B41" t="n">
-        <v>641.2105263157895</v>
+        <v>599.1666666666666</v>
       </c>
       <c r="C41" t="n">
-        <v>550.28</v>
+        <v>640.2962962962963</v>
       </c>
       <c r="D41" t="n">
-        <v>586.84</v>
+        <v>654.76</v>
       </c>
       <c r="E41" t="n">
-        <v>656.1</v>
+        <v>627.3571428571429</v>
       </c>
       <c r="F41" t="n">
-        <v>625.08</v>
+        <v>627.8461538461538</v>
       </c>
       <c r="G41" t="n">
-        <v>634.1428571428571</v>
+        <v>594.4400000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I41" t="n">
-        <v>1.125</v>
+        <v>4.5625</v>
       </c>
       <c r="J41" t="n">
-        <v>2.25</v>
+        <v>5.875</v>
       </c>
       <c r="K41" t="n">
-        <v>1.0625</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>6.25</v>
+        <v>5.9375</v>
       </c>
       <c r="O41" t="n">
         <v>1.375</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>2.875</v>
       </c>
       <c r="Q41" t="n">
+        <v>19</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
+        <v>317.4622641509434</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>55</v>
+      </c>
+      <c r="B42" t="n">
+        <v>641.2105263157895</v>
+      </c>
+      <c r="C42" t="n">
+        <v>550.28</v>
+      </c>
+      <c r="D42" t="n">
+        <v>586.84</v>
+      </c>
+      <c r="E42" t="n">
+        <v>656.1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>625.08</v>
+      </c>
+      <c r="G42" t="n">
+        <v>634.1428571428571</v>
+      </c>
+      <c r="H42" t="n">
+        <v>5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
         <v>20</v>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>female</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="T41" t="n">
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
         <v>580.4554455445544</v>
       </c>
     </row>
